--- a/Solver/Basic Solver.xlsx
+++ b/Solver/Basic Solver.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\Solver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C22EC8AB-12D9-4BD1-B1EE-F92D95E4717C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEC62B3-7360-45C4-98A2-EE284AAB368C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{D3948129-462C-4115-B5D8-4C2BEF5630EA}"/>
   </bookViews>
@@ -558,14 +558,7 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
       <c r="C2">
-        <v>850</v>
-      </c>
-      <c r="D2">
-        <f>B2*C2</f>
         <v>850</v>
       </c>
     </row>
@@ -573,15 +566,8 @@
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
       <c r="C3">
         <v>295</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D5" si="0">B3*C3</f>
-        <v>0</v>
       </c>
       <c r="I3" t="s">
         <v>6</v>
@@ -591,14 +577,7 @@
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
       <c r="C4">
-        <v>200</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
         <v>200</v>
       </c>
       <c r="I4" t="s">
@@ -609,15 +588,8 @@
       <c r="A5" t="s">
         <v>9</v>
       </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
       <c r="C5">
         <v>475</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>950</v>
       </c>
       <c r="I5" t="s">
         <v>10</v>
@@ -626,10 +598,6 @@
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="C6" t="s">
         <v>11</v>
-      </c>
-      <c r="D6">
-        <f>SUM(D2:D5)</f>
-        <v>2000</v>
       </c>
       <c r="I6" t="s">
         <v>12</v>
